--- a/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
+++ b/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Роли ДУП'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -108,10 +108,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -491,13 +491,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,10 +514,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Бизнес-владелец процесса / подпроцесса / этапа</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Роль ДУП</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Что делает ДУП</t>
         </is>
@@ -535,10 +541,15 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Директор ДУП (Аккушимов Г.В.)</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Владеет портфелем доходных проектов от приёма от ДРБ до закрытия</t>
         </is>
@@ -557,17 +568,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Зам. по строительству и реализации (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>Владеет всей фазой реализации проекта</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -579,17 +595,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Зам. по реализации — приёмка и валидация; ДРБ — передача пакета</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Принимает и проверяет комплектность пакета, регистрирует проект в портфеле</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -599,19 +620,24 @@
           <t>1.1.1  Получение карточки проекта и комплекта документов от ДРБ</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Принимает пакет, фиксирует дату и состав. Владелец процесса — ДРБ</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Принимает пакет, фиксирует дату и состав</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -623,17 +649,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по реализации</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>Проверяет комплект по чек-листу, возвращает при неполноте</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -645,17 +676,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по реализации</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>Заводит карточку проекта, присваивает код</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -665,19 +701,24 @@
           <t>1.2  Подтверждение готовности продукта (пилот)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Сегодня может только запрашивать подтверждение — процедуры нет. Целевое: владеет gate приёма. Владелец процесса — ДРБ</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ДРБ — владелец решения по продукту</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Сегодня может только запрашивать подтверждение — процедуры нет. Целевое: владеет gate приёма</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -687,19 +728,24 @@
           <t>1.2.1  Проверка завершения пилота / тестовой эксплуатации</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Запрашивает подтверждение, что пилот пройден. Владелец процесса — ДРБ</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Запрашивает подтверждение, что пилот пройден</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -711,17 +757,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Директор ДУП (целевое состояние)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>Принимает решение о старте реализации; без подписи старт блокируется</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -733,17 +784,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по реализации</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>Определяет филиал и куратора; при отсутствии филиала инициирует 3.2</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -755,17 +811,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по реализации</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>Готовит устав и план проекта совместно с филиалом</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -775,19 +836,24 @@
           <t>1.5  Формирование и согласование бюджета (ФЭМ)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Формирует финансово-экономическую модель и передаёт на согласование. Владелец процесса — Финблок</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Финблок — владелец процесса целиком</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Формирует финансово-экономическую модель и передаёт на согласование</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -797,19 +863,24 @@
           <t>1.5.1  Формирование ФЭМ по шаблону</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Готовит модель: нормативы, цены, поверка, переносы. Владелец процесса — Финблок</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Готовит модель: нормативы, цены, поверка, переносы</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -819,19 +890,24 @@
           <t>1.5.2  Проверка и согласование ФЭМ</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Даёт пояснения и корректировки по запросу Финблока. Владелец процесса — Финблок</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Даёт пояснения и корректировки по запросу Финблока</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -841,19 +917,24 @@
           <t>1.5.3  Утверждение бюджета, кредитование при необходимости</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Получает утверждённый бюджет проекта. Владелец процесса — Финблок</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Получает утверждённый бюджет проекта</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -865,17 +946,22 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по реализации</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>Сводит документы в единый приказ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -885,19 +971,24 @@
           <t>1.7  Инициация и контроль закупок</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Инициирует заявку и принимает результат поставки. Владелец процесса — Закупщики (ОЛЖА)</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА) — владелец процедуры</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует заявку и принимает результат поставки</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -907,19 +998,24 @@
           <t>1.7.1  Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Формирует заявку и план закупок, собирает тех. карты у СТ. Владелец процесса — Закупщики (ОЛЖА)</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Формирует заявку и план закупок, собирает тех. карты у СТ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -929,19 +1025,24 @@
           <t>1.7.2  Проведение процедуры закупки</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Отслеживает статус процедуры, эскалирует при просрочке. Владелец процесса — Закупщики (ОЛЖА)</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Отслеживает статус процедуры, эскалирует при просрочке</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -951,19 +1052,24 @@
           <t>1.7.3  Контроль сроков поставки и приёмка</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Контролирует сроки поставки и принимает оборудование. Владелец процесса — Закупщики (ОЛЖА)</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Контролирует сроки поставки и принимает оборудование</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -975,17 +1081,22 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по реализации</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>Ведёт регулярные статус-встречи и контроль исполнения</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -995,19 +1106,24 @@
           <t>1.9  Формирование реестра платежей и приоритизация</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Агрегирует данные филиалов, приоритизирует реестр и передаёт решение в Финблок. Владелец процесса — Финблок</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Финблок — владелец решения по оплате</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Агрегирует данные филиалов, приоритизирует реестр и передаёт решение в Финблок</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1017,19 +1133,24 @@
           <t>1.9.1  Агрегация заявок и данных филиалов</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Собирает заявки филиалов по проектам. Владелец процесса — Финблок</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Собирает заявки филиалов по проектам</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1039,19 +1160,24 @@
           <t>1.9.2  Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Расставляет приоритеты по трём потокам платежей. Владелец процесса — Финблок</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Расставляет приоритеты по трём потокам платежей</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1061,14 +1187,19 @@
           <t>1.9.3  Решение об оплате и проведение платежа</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Получает информацию о проведении платежа. Владелец процесса — Финблок</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Получает информацию о проведении платежа</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1216,22 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Зам. по операционной деятельности (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>Владеет всей фазой эксплуатации и доходности проекта</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1105,19 +1241,24 @@
           <t>2.0  Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>не назначен</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Точка передачи нигде не формализована — владелец не назначен</t>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Фактически переводит объект из реализации в сопровождение, но точка передачи нигде не формализована</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1129,17 +1270,22 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
           <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1151,17 +1297,22 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>Контролирует работоспособность канала связи объекта</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1171,19 +1322,24 @@
           <t>2.3  Прогноз поступлений / расходов и контроль бюджета</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Поставляет данные и подтверждения по проектам; результатом не владеет. Владелец процесса — Финблок</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Финблок — владелец решения и планирования</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Поставляет данные и подтверждения по проектам; результатом не владеет</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1193,19 +1349,24 @@
           <t>2.3.1  Сбор данных и подтверждений по проектам</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Собирает прогноз поступлений с филиалов. Владелец процесса — Финблок</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Собирает прогноз поступлений с филиалов</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1215,19 +1376,24 @@
           <t>2.3.2  Планирование и решение по прогнозу</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Получает утверждённый прогноз. Владелец процесса — Финблок</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Получает утверждённый прогноз</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1237,19 +1403,24 @@
           <t>2.4  Инициация продления / модернизации контракта</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Инициирует при окончании срока, собирает данные; коммерческое предложение идёт через ДРБ. Владелец процесса — ДРБ</t>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>ДРБ — владелец presale и сделки</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует при окончании срока, собирает данные; коммерческое предложение идёт через ДРБ</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1261,17 +1432,22 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
           <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1283,17 +1459,22 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Зам. по операционной деятельности — вынесение; ОСУ — решение</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
           <t>Выявляет перерасход и выносит вопрос на утверждающий орган</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1303,19 +1484,24 @@
           <t>2.7  Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>не назначен</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Должен передавать сведения от эксплуатации владельцу ТЗ и закупок. Владелец не назначен</t>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Должен передавать сведения от эксплуатации владельцу ТЗ и закупок</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1327,10 +1513,15 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Готовит ежемесячную отчётность госпартнёру и регулярную — руководству</t>
         </is>
@@ -1349,17 +1540,22 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Директор ДУП и оба зама — единого владельца нет, см. 3.1–3.3</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
           <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1371,17 +1567,22 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>Закрепляет ответственного менеджера ДУП за регионом</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1391,19 +1592,24 @@
           <t>3.2  Открытие нового филиала</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>не назначен</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>В интервью куратор ведёт открытие сам, но ни в одной из 4 ДИ обязанность не встречается. Владелец не назначен</t>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>В интервью куратор ведёт открытие сам, но ни в одной из 4 ДИ обязанность не встречается</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1415,10 +1621,15 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Оба зама ДУП — единый владелец не назначен</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
         </is>
@@ -1437,17 +1648,22 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>Главный менеджер проектов (целевой); часть функционала — за Директором ДУП</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
           <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1459,17 +1675,22 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
           <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1481,17 +1702,22 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
           <t>Проверяет полноту и корректность информации по всем проектам обоих блоков</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1503,17 +1729,22 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
           <t>Проводит аудит по трём чек-листам методологии</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
@@ -1525,10 +1756,15 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Владелец</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Готовит материалы для директора и Товарищества на уровне всего портфеля</t>
         </is>
@@ -1545,14 +1781,19 @@
           <t>Б.1  Согласование бюджета проекта / ФЭМ</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Формирует ФЭМ (подпроцесс 1.5) — это только первый этап процесса. Владелец процесса — Финблок</t>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Формирует ФЭМ (подпроцесс 1.5) — это только первый этап процесса</t>
         </is>
       </c>
     </row>
@@ -1567,19 +1808,24 @@
           <t>Б.2  Финансовое закрытие проекта</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке. Владелец процесса — Финблок</t>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1589,19 +1835,24 @@
           <t>Б.2.1  Служебная записка о необходимости закрытия</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Инициирует закрытие служебной запиской. Владелец процесса — Финблок</t>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует закрытие служебной запиской</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1611,19 +1862,24 @@
           <t>Б.2.2  Сбор актов сверок, уведомления о расторжении договоров</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Предоставляет данные по запросу. Владелец процесса — Финблок</t>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Предоставляет данные по запросу</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1633,14 +1889,19 @@
           <t>Б.2.3  Формирование бюджета на логистику / демонтаж, закрытие</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Получает подтверждение закрытия проекта. Владелец процесса — Финблок</t>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Получает подтверждение закрытия проекта</t>
         </is>
       </c>
     </row>
@@ -1655,14 +1916,19 @@
           <t>Б.3  Прогноз поступлений и расходов</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Поставляет данные и подтверждения по проектам (подпроцесс 2.3). Владелец процесса — Финблок</t>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Поставляет данные и подтверждения по проектам (подпроцесс 2.3)</t>
         </is>
       </c>
     </row>
@@ -1677,14 +1943,19 @@
           <t>Б.4  Закупки выше упрощённого порога</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Инициирует заявку и собирает спецификации; контролирует сроки и принимает поставку. Владелец процесса — Закупщики (ОЛЖА)</t>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует заявку и собирает спецификации; контролирует сроки и принимает поставку</t>
         </is>
       </c>
     </row>
@@ -1699,19 +1970,24 @@
           <t>Б.5  Открытие нового филиала</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>не назначен</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Инициирует и участвует в сборе данных; владелец не назначен</t>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует открытие филиала и участвует в сборе данных по региону</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1721,19 +1997,24 @@
           <t>Б.5.1  Инициирование, участие в сборе данных</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>не назначен</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Инициирует открытие при отсутствии филиала в регионе. Владелец не назначен</t>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует открытие при отсутствии филиала в регионе</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1743,19 +2024,24 @@
           <t>Б.5.2  Подготовка пакета документов и доверенностей</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Предоставляет данные по проекту и региону. Владелец процесса — Юр блок</t>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Предоставляет данные по проекту и региону</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
@@ -1765,14 +2051,19 @@
           <t>Б.5.3  Регистрация и запуск филиала</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>не назначен</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Участие ДУП на этапе регистрации не определено. Владелец не назначен</t>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Участие ДУП на этапе регистрации не определено</t>
         </is>
       </c>
     </row>
@@ -1787,14 +2078,19 @@
           <t>Б.6  Передача проекта от ДРБ в ДУП</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Принимает пакет и валидирует комплектность (подпроцесс 1.1). Владелец процесса — ДРБ</t>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Принимает пакет и валидирует комплектность (подпроцесс 1.1)</t>
         </is>
       </c>
     </row>
@@ -1809,14 +2105,19 @@
           <t>Б.7  Производство, монтаж и калибровка оборудования</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>Даёт требования и принимает результат; тех. карты нужны до закупки. Владелец процесса — СТ (техническая служба)</t>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>СТ (техническая служба)</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
         </is>
       </c>
     </row>
@@ -1831,19 +2132,24 @@
           <t>Б.8  Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Предоставляет условия по проекту, согласовывает проект договора. Владелец процесса — Юр блок</t>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Предоставляет условия по проекту, согласовывает проект договора</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D61"/>
+  <autoFilter ref="A1:E61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
+++ b/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Роли ДУП'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E9D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE3B3"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,6 +129,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -627,7 +635,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -708,7 +716,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -841,7 +849,7 @@
           <t>Финблок — владелец процесса целиком</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -868,7 +876,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -895,7 +903,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -924,7 +932,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -976,7 +984,7 @@
           <t>Закупщики (ОЛЖА) — владелец процедуры</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1003,7 +1011,7 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1032,7 +1040,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1059,7 +1067,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1111,7 +1119,7 @@
           <t>Финблок — владелец решения по оплате</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1138,7 +1146,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1165,7 +1173,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1194,7 +1202,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1246,7 +1254,7 @@
           <t>не назначен</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
@@ -1327,7 +1335,7 @@
           <t>Финблок — владелец решения и планирования</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1354,7 +1362,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1383,7 +1391,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1408,7 +1416,7 @@
           <t>ДРБ — владелец presale и сделки</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1489,7 +1497,7 @@
           <t>не назначен</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
@@ -1597,7 +1605,7 @@
           <t>не назначен</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
@@ -1786,7 +1794,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1813,7 +1821,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1840,7 +1848,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1867,7 +1875,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1896,7 +1904,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -1921,7 +1929,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1948,7 +1956,7 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -1975,7 +1983,7 @@
           <t>не назначен</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
@@ -2002,7 +2010,7 @@
           <t>не назначен</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
@@ -2029,7 +2037,7 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -2056,7 +2064,7 @@
           <t>не назначен</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>Не определён</t>
         </is>
@@ -2085,7 +2093,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2139,7 +2147,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2148,8 +2156,62 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Б.9  Оформление штата и кадровых приказов по проекту и филиалу</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Б.10  Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E61"/>
+  <autoFilter ref="A1:E63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
+++ b/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$63</definedName>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,11 +70,6 @@
         <fgColor rgb="00CFE0F7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBC4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -102,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -129,9 +124,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -576,7 +568,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Зам. по строительству и реализации (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
+          <t>ДУП — Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1224,7 +1216,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1251,17 +1243,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Не определён</t>
+          <t>ДУП — Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Фактически переводит объект из реализации в сопровождение, но точка передачи нигде не формализована</t>
+          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
         </is>
       </c>
     </row>
@@ -1494,17 +1486,17 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Не определён</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Должен передавать сведения от эксплуатации владельцу ТЗ и закупок</t>
+          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1540,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП и оба зама — единого владельца нет, см. 3.1–3.3</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1558,7 +1550,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
+          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Подпроцессы закреплены за директором (3.1), замом по операционной деятельности (3.2, 3.3)</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1589,22 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>3.2  Открытие нового филиала</t>
+          <t>3.2  Участие ДУП в открытии нового филиала</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Не определён</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>В интервью куратор ведёт открытие сам, но ни в одной из 4 ДИ обязанность не встречается</t>
+          <t>Отвечает за участок ДУП в открытии филиала: обоснование потребности, данные по региону, приём работающей площадки и закрепление куратора</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1621,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Оба зама ДУП — единый владелец не назначен</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1656,7 +1648,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Главный менеджер проектов (целевой); часть функционала — за Директором ДУП</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1980,17 +1972,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Не определён</t>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Инициирует открытие филиала и участвует в сборе данных по региону</t>
+          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
         </is>
       </c>
     </row>
@@ -2007,17 +1999,17 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>Не определён</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Инициирует открытие при отсутствии филиала в регионе</t>
+          <t>Обосновывает потребность в филиале и собирает данные по региону</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2053,17 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>Не определён</t>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Участие ДУП на этапе регистрации не определено</t>
+          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
         </is>
       </c>
     </row>

--- a/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
+++ b/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Роли ДУП'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Сегодня может только запрашивать подтверждение — процедуры нет. Целевое: владеет gate приёма</t>
+          <t>Сегодня может только запрашивать подтверждение. Целевое: директор ДУП подписывает gate и блокирует старт реализации, пока подписи нет</t>
         </is>
       </c>
     </row>
@@ -747,17 +747,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1.2.2  Подписание gate «продукт готов к реализации»</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>1.3  Назначение куратора (проект и филиал)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП (целевое состояние)</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Принимает решение о старте реализации; без подписи старт блокируется</t>
+          <t>Одной матрицей закрепляет куратора за проектом и за филиалом; при отсутствии филиала инициирует открытие (Б.5)</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>1.3  Назначение ответственного (куратор / филиал)</t>
+          <t>1.4  Разработка проектной документации (устав, план, приказ)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Определяет филиал и куратора; при отсутствии филиала инициирует 3.2</t>
+          <t>Готовит устав и план проекта совместно с филиалом</t>
         </is>
       </c>
     </row>
@@ -806,39 +806,39 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1.4  Разработка проектной документации (устав, план, приказ)</t>
+          <t>1.5  Формирование и согласование бюджета (ФЭМ)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок — владелец процесса целиком</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Готовит устав и план проекта совместно с филиалом</t>
+          <t>Формирует финансово-экономическую модель и передаёт на согласование</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>1.5  Формирование и согласование бюджета (ФЭМ)</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1.5.1  Формирование ФЭМ по шаблону</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Финблок — владелец процесса целиком</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Формирует финансово-экономическую модель и передаёт на согласование</t>
+          <t>Готовит модель: нормативы, цены, поверка, переносы</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>1.5.1  Формирование ФЭМ по шаблону</t>
+          <t>1.5.2  Проверка и согласование ФЭМ</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Готовит модель: нормативы, цены, поверка, переносы</t>
+          <t>Даёт пояснения и корректировки по запросу Финблока</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>1.5.2  Проверка и согласование ФЭМ</t>
+          <t>1.5.3  Утверждение бюджета, кредитование при необходимости</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -895,14 +895,14 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Даёт пояснения и корректировки по запросу Финблока</t>
+          <t>Получает утверждённый бюджет проекта</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>1.5.3  Утверждение бюджета, кредитование при необходимости</t>
+          <t>1.4.1  Оформление приказа на реализацию</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП — Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Получает утверждённый бюджет проекта</t>
+          <t>Сводит устав и план в единый приказ на реализацию</t>
         </is>
       </c>
     </row>
@@ -941,39 +941,39 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>1.6  Оформление приказа на реализацию</t>
+          <t>1.7  Инициация и контроль закупок</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Закупщики (ОЛЖА) — владелец процедуры</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Сводит документы в единый приказ</t>
+          <t>Инициирует заявку и принимает результат поставки</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>1.7  Инициация и контроль закупок</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1.7.1  Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА) — владелец процедуры</t>
+          <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Инициирует заявку и принимает результат поставки</t>
+          <t>Формирует заявку и план закупок, собирает тех. карты у СТ</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>1.7.1  Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+          <t>1.7.2  Проведение процедуры закупки</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1003,14 +1003,14 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Формирует заявку и план закупок, собирает тех. карты у СТ</t>
+          <t>Отслеживает статус процедуры, эскалирует при просрочке</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>1.7.2  Проведение процедуры закупки</t>
+          <t>1.7.3  Контроль сроков поставки и приёмка</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1037,78 +1037,78 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Отслеживает статус процедуры, эскалирует при просрочке</t>
+          <t>Контролирует сроки поставки и принимает оборудование</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>1.7.3  Контроль сроков поставки и приёмка</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>1.9  Формирование реестра платежей и приоритизация</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Финблок — владелец решения по оплате</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Контролирует сроки поставки и принимает оборудование</t>
+          <t>Агрегирует данные филиалов, приоритизирует реестр и передаёт решение в Финблок</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>1.8  Управление сроками и бюджетом проекта (статус-встречи)</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1.9.1  Агрегация заявок и данных филиалов</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Ведёт регулярные статус-встречи и контроль исполнения</t>
+          <t>Собирает заявки филиалов по проектам</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>1.9  Формирование реестра платежей и приоритизация</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1.9.2  Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Финблок — владелец решения по оплате</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Агрегирует данные филиалов, приоритизирует реестр и передаёт решение в Финблок</t>
+          <t>Расставляет приоритеты по трём потокам платежей</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>1.9.1  Агрегация заявок и данных филиалов</t>
+          <t>1.9.3  Решение об оплате и проведение платежа</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1138,85 +1138,85 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Собирает заявки филиалов по проектам</t>
+          <t>Получает информацию о проведении платежа</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>1.9.2  Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2  Постпроектное сопровождение</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Расставляет приоритеты по трём потокам платежей</t>
+          <t>Владеет всей фазой эксплуатации и доходности проекта</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>1.9.3  Решение об оплате и проведение платежа</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>2.0  Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП — Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Получает информацию о проведении платежа</t>
+          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2  Постпроектное сопровождение</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>2.1  Организация поверки оборудования</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
+          <t>ДУП — Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Владеет всей фазой эксплуатации и доходности проекта</t>
+          <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>2.0  Передача проекта «реализация → сопровождение»</t>
+          <t>2.2  Сопровождение канала связи</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по строительству и реализации</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
+          <t>Контролирует работоспособность канала связи объекта</t>
         </is>
       </c>
     </row>
@@ -1265,93 +1265,93 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>2.1  Организация поверки оборудования</t>
+          <t>2.3  Прогноз поступлений / расходов и контроль бюджета</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок — владелец решения и планирования</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
+          <t>Поставляет данные и подтверждения по проектам; результатом не владеет</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>2.2  Сопровождение канала связи</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>2.3.1  Сбор данных и подтверждений по проектам</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Контролирует работоспособность канала связи объекта</t>
+          <t>Собирает прогноз поступлений с филиалов</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>2.3  Прогноз поступлений / расходов и контроль бюджета</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>2.3.2  Планирование и решение по прогнозу</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Финблок — владелец решения и планирования</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Поставляет данные и подтверждения по проектам; результатом не владеет</t>
+          <t>Получает утверждённый прогноз</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>2.3.1  Сбор данных и подтверждений по проектам</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>2.4  Инициация продления / модернизации контракта</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>ДРБ — владелец presale и сделки</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Собирает прогноз поступлений с филиалов</t>
+          <t>Инициирует при окончании срока, собирает данные; коммерческое предложение идёт через ДРБ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>2.3.2  Планирование и решение по прогнозу</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>2.5  Обработка запросов на перенос оборудования</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Получает утверждённый прогноз</t>
+          <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1400,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>2.4  Инициация продления / модернизации контракта</t>
+          <t>2.6  Выявление нехватки бюджета и вынесение на ОСУ</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>ДРБ — владелец presale и сделки</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>Зам. по операционной деятельности — вынесение; ОСУ — решение</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Инициирует при окончании срока, собирает данные; коммерческое предложение идёт через ДРБ</t>
+          <t>Выявляет перерасход и выносит вопрос на утверждающий орган</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>2.5  Обработка запросов на перенос оборудования</t>
+          <t>2.7  Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1442,24 +1442,24 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
+          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>2.6  Выявление нехватки бюджета и вынесение на ОСУ</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>3  Управление филиальной сетью</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности — вынесение; ОСУ — решение</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Выявляет перерасход и выносит вопрос на утверждающий орган</t>
+          <t>Ведёт филиальную сеть: отношения вне проектов закреплены за замом по операционной деятельности (3.3), куратор проекта и филиала назначается одной матрицей (1.3), открытие филиала идёт сквозным маршрутом (Б.5)</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>2.7  Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+          <t>3.3  Общие отношения с филиалом (вне привязки к проекту)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1496,51 +1496,51 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
+          <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>4  Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>ДУП — Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>2.8  Отчётность руководству и госпартнёру (операционный статус)</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Готовит ежемесячную отчётность госпартнёру и регулярную — руководству</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>3  Управление филиальной сетью</t>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>4.1  Разработка и поддержка методологии, шаблонов, реестров</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Подпроцессы закреплены за директором (3.1), замом по операционной деятельности (3.2, 3.3)</t>
+          <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>3.1  Назначение куратора на филиал / проект</t>
+          <t>4.2  Контроль качества и полноты проектных данных</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Закрепляет ответственного менеджера ДУП за регионом</t>
+          <t>Проверяет полноту данных и проводит аудит по трём чек-листам: сначала один филиал, затем весь портфель</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>3.2  Участие ДУП в открытии нового филиала</t>
+          <t>4.3  Отчётность по проектам</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1604,53 +1604,53 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Отвечает за участок ДУП в открытии филиала: обоснование потребности, данные по региону, приём работающей площадки и закрепление куратора</t>
+          <t>Ведёт один контур отчётности на трёх адресатов: статус проекта, операционный статус, портфель</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>3.3  Общие отношения с филиалом (вне привязки к проекту)</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>4.3.1  Статус-встречи по проекту</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
+          <t>ДУП — Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Ведёт регулярные статус-встречи и контроль исполнения проекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>4.3.2  Операционный статус руководству и госпартнёру</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
           <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>4  Методология и контроль качества (ПМО)</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>ДУП — Главный менеджер проектов</t>
-        </is>
-      </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Владелец</t>
@@ -1658,19 +1658,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
+          <t>Готовит ежемесячную отчётность госпартнёру и регулярную — руководству</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>4.1  Разработка и поддержка методологии, шаблонов, реестров</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>4.3.3  Портфельная отчётность руководству и заказчикам</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1685,34 +1685,34 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
+          <t>Собирает портфель из проектного и операционного статуса без повторного опроса</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>4.2  Контроль качества и полноты проектных данных</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Б.2  Финансовое закрытие проекта</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Проверяет полноту и корректность информации по всем проектам обоих блоков</t>
+          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
         </is>
       </c>
     </row>
@@ -1724,61 +1724,61 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>4.2.1  Аудит проектной документации по чек-листам</t>
+          <t>Б.2.1  Служебная записка о необходимости закрытия</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Проводит аудит по трём чек-листам методологии</t>
+          <t>Инициирует закрытие служебной запиской</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>4.3  Портфельная отчётность руководству и заказчикам</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Б.2.2  Сбор актов сверок, уведомления о расторжении договоров</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Готовит материалы для директора и Товарищества на уровне всего портфеля</t>
+          <t>Предоставляет данные по запросу</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Б.1  Согласование бюджета проекта / ФЭМ</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Б.2.3  Формирование бюджета на логистику / демонтаж, закрытие</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1786,14 +1786,14 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Формирует ФЭМ (подпроцесс 1.5) — это только первый этап процесса</t>
+          <t>Получает подтверждение закрытия проекта</t>
         </is>
       </c>
     </row>
@@ -1805,22 +1805,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Б.2  Финансовое закрытие проекта</t>
+          <t>Б.5  Открытие нового филиала</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
+          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
         </is>
       </c>
     </row>
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Б.2.1  Служебная записка о необходимости закрытия</t>
+          <t>Б.5.1  Участие ДУП: потребность, данные по региону, приём площадки</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Инициирует закрытие служебной запиской</t>
+          <t>Обосновывает потребность, собирает данные по региону, принимает работающую площадку и закрепляет куратора</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Б.2.2  Сбор актов сверок, уведомления о расторжении договоров</t>
+          <t>Б.5.2  Подготовка пакета документов и доверенностей</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Предоставляет данные по запросу</t>
+          <t>Предоставляет данные по проекту и региону</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Б.2.3  Формирование бюджета на логистику / демонтаж, закрытие</t>
+          <t>Б.5.3  Регистрация и запуск филиала</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Получает подтверждение закрытия проекта</t>
+          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
         </is>
       </c>
     </row>
@@ -1913,22 +1913,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Б.3  Прогноз поступлений и расходов</t>
+          <t>Б.7  Производство, монтаж и калибровка оборудования</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>СТ (техническая служба)</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Поставляет данные и подтверждения по проектам (подпроцесс 2.3)</t>
+          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
         </is>
       </c>
     </row>
@@ -1940,22 +1940,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Б.4  Закупки выше упрощённого порога</t>
+          <t>Б.8  Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Инициирует заявку и собирает спецификации; контролирует сроки и принимает поставку</t>
+          <t>Предоставляет условия по проекту, согласовывает проект договора</t>
         </is>
       </c>
     </row>
@@ -1967,243 +1967,54 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Б.5  Открытие нового филиала</t>
+          <t>Б.9  Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
+          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Б.5.1  Инициирование, участие в сборе данных</t>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Б.10  Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Обосновывает потребность в филиале и собирает данные по региону</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Б.5.2  Подготовка пакета документов и доверенностей</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Предоставляет данные по проекту и региону</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Б.5.3  Регистрация и запуск филиала</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Б.6  Передача проекта от ДРБ в ДУП</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Принимает пакет и валидирует комплектность (подпроцесс 1.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Б.7  Производство, монтаж и калибровка оборудования</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>СТ (техническая служба)</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Б.8  Юридическое сопровождение договоров с контрагентами</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Предоставляет условия по проекту, согласовывает проект договора</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Б.9  Оформление штата и кадровых приказов по проекту и филиалу</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Б.10  Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Зерек (ИТ-инфраструктура)</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
           <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E63"/>
+  <autoFilter ref="A1:E56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
+++ b/dup_project/01_Процессы/ДУП_роли_в_процессах_кратко.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Роли ДУП" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Роли ДУП'!$A$1:$E$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Роли ДУП'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -536,12 +536,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ДУП.0  Управление проектами (ГЧП / ГЗ)</t>
+          <t>1  Реализация проекта</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП (Аккушимов Г.В.)</t>
+          <t>ДУП — Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -551,24 +551,24 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Владеет портфелем доходных проектов от приёма от ДРБ до закрытия</t>
+          <t>Владеет всей фазой реализации проекта</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1  Реализация проекта</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>1.1  Приём и валидация пакета документов от ДРБ</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по строительству и реализации</t>
+          <t>Зам. по реализации — приёмка и валидация; ДРБ — передача пакета</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -578,34 +578,34 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Владеет всей фазой реализации проекта</t>
+          <t>Принимает и проверяет комплектность пакета, регистрирует проект в портфеле</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>1.1  Приём и валидация пакета документов от ДРБ</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>1.1.1  Получение карточки проекта и комплекта документов от ДРБ</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Зам. по реализации — приёмка и валидация; ДРБ — передача пакета</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Принимает и проверяет комплектность пакета, регистрирует проект в портфеле</t>
+          <t>Принимает пакет, фиксирует дату и состав</t>
         </is>
       </c>
     </row>
@@ -617,22 +617,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>1.1.1  Получение карточки проекта и комплекта документов от ДРБ</t>
+          <t>1.1.2  Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП — Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Принимает пакет, фиксирует дату и состав</t>
+          <t>Проверяет комплект по чек-листу, возвращает при неполноте</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>1.1.2  Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
+          <t>1.1.3  Регистрация проекта в портфеле / системе</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -659,34 +659,34 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Проверяет комплект по чек-листу, возвращает при неполноте</t>
+          <t>Заводит карточку проекта, присваивает код</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1.1.3  Регистрация проекта в портфеле / системе</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>ГП  Вывод продукта в реализацию</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>ДРБ — владелец решения по продукту</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Заводит карточку проекта, присваивает код</t>
+          <t>Запрашивает подтверждение готовности и принимает решение, можно ли стартовать реализацию</t>
         </is>
       </c>
     </row>
@@ -799,14 +799,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>1.5  Формирование и согласование бюджета (ФЭМ)</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>БЖ  Бюджетирование проекта</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -821,24 +821,24 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Формирует финансово-экономическую модель и передаёт на согласование</t>
+          <t>Готовит финансово-экономическую модель и передаёт её на согласование</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>1.5.1  Формирование ФЭМ по шаблону</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>1.5  Формирование и согласование бюджета (ФЭМ)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Финблок — владелец процесса целиком</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Готовит модель: нормативы, цены, поверка, переносы</t>
+          <t>Формирует финансово-экономическую модель и передаёт на согласование</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>1.5.2  Проверка и согласование ФЭМ</t>
+          <t>1.5.1  Формирование ФЭМ по шаблону</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Даёт пояснения и корректировки по запросу Финблока</t>
+          <t>Готовит модель: нормативы, цены, поверка, переносы</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>1.5.3  Утверждение бюджета, кредитование при необходимости</t>
+          <t>1.5.2  Проверка и согласование ФЭМ</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -895,14 +895,14 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Получает утверждённый бюджет проекта</t>
+          <t>Даёт пояснения и корректировки по запросу Финблока</t>
         </is>
       </c>
     </row>
@@ -914,103 +914,103 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>1.4.1  Оформление приказа на реализацию</t>
+          <t>1.5.3  Утверждение бюджета, кредитование при необходимости</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Сводит устав и план в единый приказ на реализацию</t>
+          <t>Получает утверждённый бюджет проекта</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>1.7  Инициация и контроль закупок</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1.4.1  Оформление приказа на реализацию</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>ДУП — Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Сводит устав и план в единый приказ на реализацию</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>ЗК  Осуществление закупок</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
           <t>Закупщики (ОЛЖА) — владелец процедуры</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Инициирует заявку и принимает результат поставки</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>1.7.1  Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Формирует заявку и план закупок, собирает тех. карты у СТ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>1.7.2  Проведение процедуры закупки</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1.7  Инициация и контроль закупок</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Закупщики (ОЛЖА) — владелец процедуры</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Отслеживает статус процедуры, эскалирует при просрочке</t>
+          <t>Инициирует заявку и принимает результат поставки</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>1.7.3  Контроль сроков поставки и приёмка</t>
+          <t>1.7.1  Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1030,41 +1030,41 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Контролирует сроки поставки и принимает оборудование</t>
+          <t>Формирует заявку и план закупок, собирает тех. карты у СТ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>1.9  Формирование реестра платежей и приоритизация</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1.7.2  Проведение процедуры закупки</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Финблок — владелец решения по оплате</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Агрегирует данные филиалов, приоритизирует реестр и передаёт решение в Финблок</t>
+          <t>Отслеживает статус процедуры, эскалирует при просрочке</t>
         </is>
       </c>
     </row>
@@ -1076,169 +1076,169 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>1.9.1  Агрегация заявок и данных филиалов</t>
+          <t>1.7.3  Контроль сроков поставки и приёмка</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Контролирует сроки поставки и принимает оборудование</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ПЛ  Проведение платежей по проектам</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Финблок — владелец решения по оплате</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Собирает заявки филиалов по проектам</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>1.9.2  Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Расставляет приоритеты по трём потокам платежей</t>
+          <t>Собирает заявки, расставляет приоритеты и передаёт реестр на оплату</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>1.9.3  Решение об оплате и проведение платежа</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>1.9  Формирование реестра платежей и приоритизация</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
+          <t>Финблок — владелец решения по оплате</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Агрегирует данные филиалов, приоритизирует реестр и передаёт решение в Финблок</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1.9.1  Агрегация заявок и данных филиалов</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Получает информацию о проведении платежа</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>2  Постпроектное сопровождение</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Владеет всей фазой эксплуатации и доходности проекта</t>
+          <t>Собирает заявки филиалов по проектам</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>2.0  Передача проекта «реализация → сопровождение»</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1.9.2  Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по строительству и реализации</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
+          <t>Расставляет приоритеты по трём потокам платежей</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>2.1  Организация поверки оборудования</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1.9.3  Решение об оплате и проведение платежа</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
+          <t>Получает информацию о проведении платежа</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>2.2  Сопровождение канала связи</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2  Постпроектное сопровождение</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Контролирует работоспособность канала связи объекта</t>
+          <t>Владеет всей фазой эксплуатации и доходности проекта</t>
         </is>
       </c>
     </row>
@@ -1265,93 +1265,93 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>2.3  Прогноз поступлений / расходов и контроль бюджета</t>
+          <t>2.0  Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Финблок — владелец решения и планирования</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Поставляет данные и подтверждения по проектам; результатом не владеет</t>
+          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>2.3.1  Сбор данных и подтверждений по проектам</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>2.1  Организация поверки оборудования</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Собирает прогноз поступлений с филиалов</t>
+          <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>2.3.2  Планирование и решение по прогнозу</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>2.2  Сопровождение канала связи</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Получает утверждённый прогноз</t>
+          <t>Контролирует работоспособность канала связи объекта</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>2.4  Инициация продления / модернизации контракта</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>ПР  Прогноз и контроль бюджета</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>ДРБ — владелец presale и сделки</t>
+          <t>Финблок — владелец решения и планирования</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Инициирует при окончании срока, собирает данные; коммерческое предложение идёт через ДРБ</t>
+          <t>Поставляет данные по проектам и выносит нехватку бюджета на утверждение</t>
         </is>
       </c>
     </row>
@@ -1373,76 +1373,76 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>2.5  Обработка запросов на перенос оборудования</t>
+          <t>2.3  Прогноз поступлений / расходов и контроль бюджета</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок — владелец решения и планирования</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
+          <t>Поставляет данные и подтверждения по проектам; результатом не владеет</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>2.6  Выявление нехватки бюджета и вынесение на ОСУ</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>2.3.1  Сбор данных и подтверждений по проектам</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности — вынесение; ОСУ — решение</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Выявляет перерасход и выносит вопрос на утверждающий орган</t>
+          <t>Собирает прогноз поступлений с филиалов</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>2.7  Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>2.3.2  Планирование и решение по прогнозу</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
+          <t>Получает утверждённый прогноз</t>
         </is>
       </c>
     </row>
@@ -1454,22 +1454,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>3  Управление филиальной сетью</t>
+          <t>КН  Продление и модернизация контракта</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>ДРБ — владелец presale и сделки</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Ведёт филиальную сеть: отношения вне проектов закреплены за замом по операционной деятельности (3.3), куратор проекта и филиала назначается одной матрицей (1.3), открытие филиала идёт сквозным маршрутом (Б.5)</t>
+          <t>Инициирует продление при окончании срока и передаёт данные для сделки</t>
         </is>
       </c>
     </row>
@@ -1481,41 +1481,41 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>3.3  Общие отношения с филиалом (вне привязки к проекту)</t>
+          <t>2.4  Инициация продления / модернизации контракта</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
+          <t>ДРБ — владелец presale и сделки</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Инициирует при окончании срока, собирает данные; коммерческое предложение идёт через ДРБ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>2.5  Обработка запросов на перенос оборудования</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
           <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>4  Методология и контроль качества (ПМО)</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>ДУП — Главный менеджер проектов</t>
-        </is>
-      </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Владелец</t>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
+          <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>4.1  Разработка и поддержка методологии, шаблонов, реестров</t>
+          <t>2.6  Выявление нехватки бюджета и вынесение на ОСУ</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Главный менеджер проектов</t>
+          <t>Зам. по операционной деятельности — вынесение; ОСУ — решение</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
+          <t>Выявляет перерасход и выносит вопрос на утверждающий орган</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>4.2  Контроль качества и полноты проектных данных</t>
+          <t>2.7  Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Главный менеджер проектов</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1577,24 +1577,24 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Проверяет полноту данных и проводит аудит по трём чек-листам: сначала один филиал, затем весь портфель</t>
+          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>4.3  Отчётность по проектам</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>3  Управление филиальной сетью</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Главный менеджер проектов</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Ведёт один контур отчётности на трёх адресатов: статус проекта, операционный статус, портфель</t>
+          <t>Ведёт филиальную сеть: отношения вне проектов закреплены за замом по операционной деятельности (3.3), куратор проекта и филиала назначается одной матрицей (1.3), открытие филиала идёт сквозным маршрутом (Б.5)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>4.3.1  Статус-встречи по проекту</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>3.3  Общие отношения с филиалом (вне привязки к проекту)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по реализации</t>
+          <t>ДУП — Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1631,24 +1631,24 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Ведёт регулярные статус-встречи и контроль исполнения проекта</t>
+          <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>4.3.2  Операционный статус руководству и госпартнёру</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>4  Методология и контроль качества (ПМО)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
+          <t>ДУП — Главный менеджер проектов</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Готовит ежемесячную отчётность госпартнёру и регулярную — руководству</t>
+          <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>4.3.3  Портфельная отчётность руководству и заказчикам</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>4.1  Разработка и поддержка методологии, шаблонов, реестров</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1685,61 +1685,61 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Собирает портфель из проектного и операционного статуса без повторного опроса</t>
+          <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Б.2  Финансовое закрытие проекта</t>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>4.2  Контроль качества и полноты проектных данных</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
+          <t>Проверяет полноту данных и проводит аудит по трём чек-листам: сначала один филиал, затем весь портфель</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Б.2.1  Служебная записка о необходимости закрытия</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>4.3  Отчётность по проектам</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Инициирует закрытие служебной запиской</t>
+          <t>Ведёт один контур отчётности на трёх адресатов: статус проекта, операционный статус, портфель</t>
         </is>
       </c>
     </row>
@@ -1751,22 +1751,22 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Б.2.2  Сбор актов сверок, уведомления о расторжении договоров</t>
+          <t>4.3.1  Статус-встречи по проекту</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП — Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Предоставляет данные по запросу</t>
+          <t>Ведёт регулярные статус-встречи и контроль исполнения проекта</t>
         </is>
       </c>
     </row>
@@ -1778,76 +1778,76 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Б.2.3  Формирование бюджета на логистику / демонтаж, закрытие</t>
+          <t>4.3.2  Операционный статус руководству и госпартнёру</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Готовит ежемесячную отчётность госпартнёру и регулярную — руководству</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>4.3.3  Портфельная отчётность руководству и заказчикам</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>ДУП — Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Собирает портфель из проектного и операционного статуса без повторного опроса</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Б.2  Финансовое закрытие проекта</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
           <t>Финблок</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Получает подтверждение закрытия проекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Б.5  Открытие нового филиала</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Директор ДУП</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Б.5.1  Участие ДУП: потребность, данные по региону, приём площадки</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>ДУП — Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Обосновывает потребность, собирает данные по региону, принимает работающую площадку и закрепляет куратора</t>
+          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Б.5.2  Подготовка пакета документов и доверенностей</t>
+          <t>Б.2.1  Служебная записка о необходимости закрытия</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Предоставляет данные по проекту и региону</t>
+          <t>Инициирует закрытие служебной запиской</t>
         </is>
       </c>
     </row>
@@ -1886,49 +1886,49 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Б.5.3  Регистрация и запуск филиала</t>
+          <t>Б.2.2  Сбор актов сверок, уведомления о расторжении договоров</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Предоставляет данные по запросу</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Б.2.3  Формирование бюджета на логистику / демонтаж, закрытие</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Б.7  Производство, монтаж и калибровка оборудования</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>СТ (техническая служба)</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
+          <t>Получает подтверждение закрытия проекта</t>
         </is>
       </c>
     </row>
@@ -1940,81 +1940,216 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
+          <t>Б.5  Открытие нового филиала</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Б.5.1  Участие ДУП: потребность, данные по региону, приём площадки</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ДУП — Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Обосновывает потребность, собирает данные по региону, принимает работающую площадку и закрепляет куратора</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Б.5.2  Подготовка пакета документов и доверенностей</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Предоставляет данные по проекту и региону</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Б.5.3  Регистрация и запуск филиала</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Б.7  Производство, монтаж и калибровка оборудования</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>СТ (техническая служба)</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>Б.8  Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Предоставляет условия по проекту, согласовывает проект договора</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Б.9  Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Б.10  Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Зерек (ИТ-инфраструктура)</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E56"/>
+  <autoFilter ref="A1:E61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
